--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T10:55:45+00:00</t>
+    <t>2023-04-05T15:18:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:18:36+00:00</t>
+    <t>2023-04-05T15:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:41:27+00:00</t>
+    <t>2023-04-05T15:52:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:52:08+00:00</t>
+    <t>2023-04-05T15:53:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:53:16+00:00</t>
+    <t>2023-04-05T15:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:55:13+00:00</t>
+    <t>2023-04-05T16:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:00:25+00:00</t>
+    <t>2023-04-05T16:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:20:25+00:00</t>
+    <t>2023-04-05T16:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:21:30+00:00</t>
+    <t>2023-04-05T16:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T17:39:15+00:00</t>
+    <t>2023-04-07T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-07T12:42:40+00:00</t>
+    <t>2023-04-12T10:00:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:00:48+00:00</t>
+    <t>2023-04-12T10:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:05:52+00:00</t>
+    <t>2023-04-12T10:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T07:49:09+00:00</t>
+    <t>2023-04-13T08:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:12:13+00:00</t>
+    <t>2023-04-13T08:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:22:34+00:00</t>
+    <t>2023-04-13T08:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:34:34+00:00</t>
+    <t>2023-04-13T08:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:54:00+00:00</t>
+    <t>2023-04-13T09:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1499,10 +1499,10 @@
 </t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS</t>
-  </si>
-  <si>
-    <t>mailboxMSS</t>
+    <t>PractitionerRole.extension:as-mailbox-mss</t>
+  </si>
+  <si>
+    <t>as-mailbox-mss</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-mailbox-mss}
@@ -1515,13 +1515,13 @@
     <t>BALs MSS de type PER rattaché à l'identifiant du professionnel de santé  ainsi qu'au lieu de sa situation d'exercice</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:value</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:value</t>
   </si>
   <si>
     <t>value</t>
@@ -1530,34 +1530,34 @@
     <t>BAL MSS</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:value.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:value.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:value.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:value.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:type</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:value.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:value.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:value.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:value.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:type</t>
   </si>
   <si>
     <t>type</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:type.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:type.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:type.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:type.value[x]</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:type.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:type.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:type.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:type.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -1567,7 +1567,7 @@
     <t>closed</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:type.value[x]:valueCodeableConcept</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:type.value[x]:valueCodeableConcept</t>
   </si>
   <si>
     <t>valueCodeableConcept</t>
@@ -1585,67 +1585,67 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:description</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:description</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:description.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:description.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:description.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:description.value[x]</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:description.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:description.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:description.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:description.value[x]</t>
   </si>
   <si>
     <t>Description fonctionnelle de la boîte aux lettres</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:responsible</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:responsible</t>
   </si>
   <si>
     <t>responsible</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:responsible.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:responsible.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:responsible.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:responsible.value[x]</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:responsible.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:responsible.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:responsible.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:responsible.value[x]</t>
   </si>
   <si>
     <t>Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:service</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:service</t>
   </si>
   <si>
     <t>service</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:service.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:service.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:service.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:service.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:service.value[x]:valueString</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:service.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:service.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:service.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:service.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:service.value[x]:valueString</t>
   </si>
   <si>
     <t>valueString</t>
@@ -1654,49 +1654,49 @@
     <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:phone</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:phone</t>
   </si>
   <si>
     <t>phone</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:phone.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:phone.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:phone.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:phone.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:phone.value[x]:valueString</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:phone.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:phone.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:phone.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:phone.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:phone.value[x]:valueString</t>
   </si>
   <si>
     <t>Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:digitization</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:digitization</t>
   </si>
   <si>
     <t>digitization</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:digitization.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:digitization.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:digitization.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:digitization.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:digitization.value[x]:valueBoolean</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:digitization.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:digitization.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:digitization.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:digitization.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:digitization.value[x]:valueBoolean</t>
   </si>
   <si>
     <t>valueBoolean</t>
@@ -1709,25 +1709,25 @@
 - N : Dématérialisation refusée</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:publication</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:publication</t>
   </si>
   <si>
     <t>publication</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:publication.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:publication.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:publication.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:publication.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:publication.value[x]:valueBoolean</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:publication.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:publication.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:publication.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:publication.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:publication.value[x]:valueBoolean</t>
   </si>
   <si>
     <t>ndicateur liste rouge</t>
@@ -1737,31 +1737,31 @@
 N: La boîte aux lettres peut être publiée</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:date</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:date</t>
   </si>
   <si>
     <t>date</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:date.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:date.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:date.url</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.extension:date.value[x]</t>
-  </si>
-  <si>
-    <t>PractitionerRole.extension:mailboxMSS.url</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:date.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:date.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:date.url</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.extension:date.value[x]</t>
+  </si>
+  <si>
+    <t>PractitionerRole.extension:as-mailbox-mss.url</t>
   </si>
   <si>
     <t>http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-mailbox-mss</t>
   </si>
   <si>
-    <t>PractitionerRole.extension:mailboxMSS.value[x]</t>
+    <t>PractitionerRole.extension:as-mailbox-mss.value[x]</t>
   </si>
   <si>
     <t>PractitionerRole.modifierExtension</t>
@@ -10303,7 +10303,7 @@
         <v>85</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>75</v>
@@ -16433,7 +16433,7 @@
         <v>85</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>75</v>
@@ -16547,7 +16547,7 @@
         <v>85</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>75</v>
@@ -16625,7 +16625,7 @@
         <v>97</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T09:51:53+00:00</t>
+    <t>2023-04-13T10:21:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10303,7 +10303,7 @@
         <v>85</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>75</v>
@@ -16547,7 +16547,7 @@
         <v>85</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>75</v>
@@ -16625,7 +16625,7 @@
         <v>97</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T10:21:56+00:00</t>
+    <t>2023-04-13T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10303,7 +10303,7 @@
         <v>85</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>75</v>
@@ -16547,7 +16547,7 @@
         <v>85</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>75</v>
@@ -16625,7 +16625,7 @@
         <v>97</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T12:58:26+00:00</t>
+    <t>2023-04-13T15:00:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -23525,7 +23525,7 @@
         <v>97</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>615</v>
@@ -23901,7 +23901,7 @@
         <v>85</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>75</v>
@@ -24019,7 +24019,7 @@
         <v>85</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>75</v>
@@ -24941,7 +24941,7 @@
         <v>85</v>
       </c>
       <c r="H189" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I189" t="s" s="2">
         <v>75</v>
@@ -25863,7 +25863,7 @@
         <v>85</v>
       </c>
       <c r="H197" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I197" t="s" s="2">
         <v>75</v>
@@ -26785,7 +26785,7 @@
         <v>85</v>
       </c>
       <c r="H205" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I205" t="s" s="2">
         <v>75</v>
@@ -27707,7 +27707,7 @@
         <v>85</v>
       </c>
       <c r="H213" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I213" t="s" s="2">
         <v>75</v>
@@ -27825,7 +27825,7 @@
         <v>85</v>
       </c>
       <c r="H214" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I214" t="s" s="2">
         <v>75</v>
@@ -28297,7 +28297,7 @@
         <v>85</v>
       </c>
       <c r="H218" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I218" t="s" s="2">
         <v>75</v>
@@ -29219,7 +29219,7 @@
         <v>85</v>
       </c>
       <c r="H226" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I226" t="s" s="2">
         <v>75</v>
@@ -30141,7 +30141,7 @@
         <v>85</v>
       </c>
       <c r="H234" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I234" t="s" s="2">
         <v>75</v>
@@ -31063,7 +31063,7 @@
         <v>85</v>
       </c>
       <c r="H242" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I242" t="s" s="2">
         <v>75</v>
@@ -31181,7 +31181,7 @@
         <v>85</v>
       </c>
       <c r="H243" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I243" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:00:08+00:00</t>
+    <t>2023-04-13T15:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -47486,10 +47486,10 @@
         <v>76</v>
       </c>
       <c r="G385" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H385" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I385" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:16:05+00:00</t>
+    <t>2023-04-14T12:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -47600,10 +47600,10 @@
         <v>76</v>
       </c>
       <c r="G386" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H386" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I386" t="s" s="2">
         <v>75</v>
@@ -47714,10 +47714,10 @@
         <v>76</v>
       </c>
       <c r="G387" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H387" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I387" t="s" s="2">
         <v>75</v>
@@ -47828,10 +47828,10 @@
         <v>76</v>
       </c>
       <c r="G388" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H388" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I388" t="s" s="2">
         <v>75</v>
@@ -48738,10 +48738,10 @@
         <v>76</v>
       </c>
       <c r="G396" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H396" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I396" t="s" s="2">
         <v>75</v>
@@ -49420,10 +49420,10 @@
         <v>76</v>
       </c>
       <c r="G402" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H402" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I402" t="s" s="2">
         <v>75</v>
@@ -49534,10 +49534,10 @@
         <v>76</v>
       </c>
       <c r="G403" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H403" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I403" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:31:23+00:00</t>
+    <t>2023-04-14T12:45:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -22864,10 +22864,10 @@
         <v>76</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>75</v>
@@ -23096,10 +23096,10 @@
         <v>76</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:45:28+00:00</t>
+    <t>2023-04-14T13:02:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -27940,10 +27940,10 @@
         <v>76</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H215" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I215" t="s" s="2">
         <v>75</v>
@@ -28058,10 +28058,10 @@
         <v>76</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H216" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I216" t="s" s="2">
         <v>75</v>
@@ -28176,10 +28176,10 @@
         <v>76</v>
       </c>
       <c r="G217" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H217" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I217" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:02:26+00:00</t>
+    <t>2023-04-14T13:12:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6417,7 +6417,7 @@
         <v>97</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
@@ -7244,10 +7244,10 @@
         <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:12:31+00:00</t>
+    <t>2023-04-17T08:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:17:23+00:00</t>
+    <t>2023-04-17T08:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6428,10 +6428,10 @@
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>75</v>
@@ -6994,10 +6994,10 @@
         <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>75</v>
@@ -7560,10 +7560,10 @@
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>75</v>
@@ -8126,10 +8126,10 @@
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:37:32+00:00</t>
+    <t>2023-04-17T09:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9030,10 +9030,10 @@
         <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>75</v>
@@ -10394,10 +10394,10 @@
         <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>75</v>
@@ -10960,10 +10960,10 @@
         <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>75</v>
@@ -11526,10 +11526,10 @@
         <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>75</v>
@@ -12092,10 +12092,10 @@
         <v>76</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>75</v>
@@ -12658,10 +12658,10 @@
         <v>76</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>75</v>
@@ -15274,10 +15274,10 @@
         <v>76</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>75</v>
@@ -17306,7 +17306,7 @@
         <v>76</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>86</v>
@@ -18546,7 +18546,7 @@
         <v>76</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>86</v>
@@ -20578,10 +20578,10 @@
         <v>76</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:39:40+00:00</t>
+    <t>2023-04-17T10:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:56:20+00:00</t>
+    <t>2023-04-17T11:14:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:14:19+00:00</t>
+    <t>2023-04-17T11:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T13:37:35+00:00</t>
+    <t>2023-04-17T14:05:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T14:05:09+00:00</t>
+    <t>2023-04-20T17:39:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:42:03+00:00</t>
+    <t>2023-04-20T17:43:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:10+00:00</t>
+    <t>2023-04-20T17:43:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:52+00:00</t>
+    <t>2023-04-28T11:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:09:12+00:00</t>
+    <t>2023-04-28T15:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T15:03:41+00:00</t>
+    <t>2023-04-28T18:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:35:22+00:00</t>
+    <t>2023-04-28T18:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:37:07+00:00</t>
+    <t>2023-04-28T18:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4787,7 +4787,7 @@
         <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>75</v>
@@ -5129,7 +5129,7 @@
         <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>75</v>
@@ -20451,7 +20451,7 @@
         <v>77</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I155" t="s" s="2">
         <v>75</v>
@@ -21829,7 +21829,7 @@
         <v>77</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>75</v>
@@ -23207,7 +23207,7 @@
         <v>77</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>75</v>
@@ -24585,7 +24585,7 @@
         <v>77</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>75</v>
@@ -25963,7 +25963,7 @@
         <v>77</v>
       </c>
       <c r="H203" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I203" t="s" s="2">
         <v>75</v>
@@ -27341,7 +27341,7 @@
         <v>77</v>
       </c>
       <c r="H215" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I215" t="s" s="2">
         <v>75</v>
@@ -28719,7 +28719,7 @@
         <v>77</v>
       </c>
       <c r="H227" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I227" t="s" s="2">
         <v>75</v>
@@ -30097,7 +30097,7 @@
         <v>77</v>
       </c>
       <c r="H239" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I239" t="s" s="2">
         <v>75</v>
@@ -31475,7 +31475,7 @@
         <v>77</v>
       </c>
       <c r="H251" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I251" t="s" s="2">
         <v>75</v>
@@ -32853,7 +32853,7 @@
         <v>77</v>
       </c>
       <c r="H263" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I263" t="s" s="2">
         <v>75</v>
@@ -34231,7 +34231,7 @@
         <v>77</v>
       </c>
       <c r="H275" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I275" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:58:16+00:00</t>
+    <t>2023-05-02T06:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:31:09+00:00</t>
+    <t>2023-05-02T06:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:04:27+00:00</t>
+    <t>2023-05-02T14:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:10:11+00:00</t>
+    <t>2023-05-02T14:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:20:51+00:00</t>
+    <t>2023-05-02T14:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T15:50:41+00:00</t>
+    <t>2023-05-02T16:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2069,7 +2069,7 @@
 </t>
   </si>
   <si>
-    <t>The location(s) at which this practitioner provides care</t>
+    <t>idLocation</t>
   </si>
   <si>
     <t>The location(s) at which this practitioner provides care.</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T16:15:55+00:00</t>
+    <t>2023-05-02T17:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:25:18+00:00</t>
+    <t>2023-05-02T17:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:45:11+00:00</t>
+    <t>2023-05-02T17:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:01:59+00:00</t>
+    <t>2023-05-04T14:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:04:48+00:00</t>
+    <t>2023-05-04T14:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
